--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1123,6 +1123,76 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TbArcheryConfig</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ArcheryConfig</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>#ArcheryConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ArcheryConfig(활쏘기 웨이브 튜닝)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TbArcheryTarget</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ArcheryTargetKind</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>#ArcheryTarget.xlsx</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ArcheryTargetKind(과녁 종류)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,6 +1193,41 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TbArcheryRing</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ArcheryRing</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>#ArcheryRing.xlsx</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ArcheryRing(과녁 동심원 띠)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1228,6 +1228,45 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TbArcheryRange</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ArcheryRange</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>#ArcheryRange.xlsx</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ArcheryRange(사거리 맵의 거리별 노출)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1229,7 +1229,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>TbArcheryRange</t>
@@ -1258,14 +1257,46 @@
           <t>map</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>ArcheryRange(사거리 맵의 거리별 노출)</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TbDodgeConfig</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DodgeConfig</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>#DodgeConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>DodgeConfig(피하기 목숨·판정·위험 튜닝, 클서 공용)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1298,6 +1298,41 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TbDodgeStage</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DodgeStage</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>#DodgeStage.xlsx</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>DodgeStage(피하기 스테이지 순서·길이·종류·세기, 클서 공용)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,7 +974,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>c,s,m</t>
+          <t>c,s,m,l</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1330,6 +1330,126 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>DodgeStage(피하기 스테이지 순서·길이·종류·세기, 클서 공용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TbRankDivision</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>RankDivision</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>#RankDivision.xlsx</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>c,l</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>RankDivision(랭크 단계·숨은 점수 하한·감소)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TbRankConfig</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>RankConfig</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>#RankConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>RankConfig(랭크 LP·강등·배치 규칙)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TbRankSeason</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>RankSeason</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>#RankSeason.xlsx</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>RankSeason(시즌·구간·초기화)</t>
         </is>
       </c>
     </row>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1453,6 +1453,206 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TbCurrency</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>#Currency.xlsx</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>c,l</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>재화 종류</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TbCosmeticSlot</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CosmeticSlot</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>#CosmeticSlot.xlsx</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>c,l</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>꾸밈 슬롯</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TbCosmetic</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Cosmetic</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>#Cosmetic.xlsx</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>c,l</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>꾸밈 품목</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TbEconomyConfig</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EconomyConfig</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>#EconomyConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>지급 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TbLevelCurve</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>LevelCurve</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>#LevelCurve.xlsx</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>레벨 곡선</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1653,6 +1653,46 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TbAppearanceColor</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AppearanceColor</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>#AppearanceColor.xlsx</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>c,l</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>외형 색표(피부·머리)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1693,6 +1693,41 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TbMountedArcheryConfig</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MountedArcheryConfig</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>#MountedArcheryConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>MountedArcheryConfig(말 위 활쏘기 탈것·화살 튜닝, 클서 공용)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,6 +1728,41 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TbMountedArcheryZone</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MountedArcheryZone</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>#MountedArcheryZone.xlsx</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>MountedArcheryZone(말 위 활쏘기 원 단계: 쉼·축소·끝 반지름·초당 피해, 클서 공용)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1763,6 +1763,41 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TbKnockbackConfig</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>KnockbackConfig</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>#KnockbackConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>KnockbackConfig(넉백 생존전 튜닝, 클서 공용)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,6 +1838,41 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TbKnockbackZone</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>KnockbackZone</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>#KnockbackZone.xlsx</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>KnockbackZone(넉백 생존전 원 단계: 쉼·축소·끝 반지름, 클서 공용)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1798,6 +1798,41 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TbKnockbackZone</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>KnockbackZone</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>#KnockbackZone.xlsx</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>KnockbackZone(넉백 생존전 원 단계: 쉼·축소·끝 반지름, 클서 공용)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/__tables__.xlsx
+++ b/table/Datas/__tables__.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1798,6 +1798,46 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TbQuest</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Quest</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>#Quest.xlsx</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>퀘스트(일일·주간) 목록</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
